--- a/artfynd/A 59467-2020 artfynd.xlsx
+++ b/artfynd/A 59467-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,128 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113606894</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57963</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gökskulla, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>330191</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6398292</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Landvetter</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Romklumpar i större körskada. Calluna AB (EEN0055).</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59467-2020 artfynd.xlsx
+++ b/artfynd/A 59467-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113595576</v>
       </c>
       <c r="B2" t="n">
-        <v>56029</v>
+        <v>56036</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>113606894</v>
       </c>
       <c r="B3" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59467-2020 artfynd.xlsx
+++ b/artfynd/A 59467-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113595576</v>
       </c>
       <c r="B2" t="n">
-        <v>56036</v>
+        <v>56038</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>113606894</v>
       </c>
       <c r="B3" t="n">
-        <v>57964</v>
+        <v>57966</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59467-2020 artfynd.xlsx
+++ b/artfynd/A 59467-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113595576</v>
       </c>
       <c r="B2" t="n">
-        <v>56038</v>
+        <v>56066</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>113606894</v>
       </c>
       <c r="B3" t="n">
-        <v>57966</v>
+        <v>57994</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59467-2020 artfynd.xlsx
+++ b/artfynd/A 59467-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
